--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42554,6 +42554,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1835">
+      <c r="A1835" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>16250</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>32.2999992370605</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>33.2999992370605</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="G1835" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42577,6 +42577,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1836">
+      <c r="A1836" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>19000</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="G1836" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42588,7 +42588,7 @@
         <v>33.5</v>
       </c>
       <c r="D1836" t="n">
-        <v>30.2000007629395</v>
+        <v>29.7000007629395</v>
       </c>
       <c r="E1836" t="n">
         <v>33.5</v>
@@ -42597,6 +42597,29 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1836" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>55000</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>29.8999996185303</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>27</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>29.8999996185303</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>27.7999992370605</v>
+      </c>
+      <c r="G1837" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42623,6 +42623,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>45250</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>27.7000007629395</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>27.7000007629395</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1838" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42464,22 +42464,22 @@
     </row>
     <row r="1831">
       <c r="A1831" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1831" t="n">
-        <v>11000</v>
+        <v>12250</v>
       </c>
       <c r="C1831" t="n">
-        <v>42.2999992370605</v>
+        <v>45.0999984741211</v>
       </c>
       <c r="D1831" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="E1831" t="n">
-        <v>41</v>
+        <v>44.9000015258789</v>
       </c>
       <c r="F1831" t="n">
-        <v>41.7999992370605</v>
+        <v>42.5</v>
       </c>
       <c r="G1831" t="s">
         <v>7</v>
@@ -42487,22 +42487,22 @@
     </row>
     <row r="1832">
       <c r="A1832" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1832" t="n">
-        <v>24250</v>
+        <v>11000</v>
       </c>
       <c r="C1832" t="n">
-        <v>41.9000015258789</v>
+        <v>42.2999992370605</v>
       </c>
       <c r="D1832" t="n">
-        <v>37.7000007629395</v>
+        <v>41</v>
       </c>
       <c r="E1832" t="n">
-        <v>41.7000007629395</v>
+        <v>41</v>
       </c>
       <c r="F1832" t="n">
-        <v>39.0999984741211</v>
+        <v>41.7999992370605</v>
       </c>
       <c r="G1832" t="s">
         <v>7</v>
@@ -42510,22 +42510,22 @@
     </row>
     <row r="1833">
       <c r="A1833" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1833" t="n">
-        <v>44500</v>
+        <v>24250</v>
       </c>
       <c r="C1833" t="n">
-        <v>39</v>
+        <v>41.9000015258789</v>
       </c>
       <c r="D1833" t="n">
-        <v>33</v>
+        <v>37.7000007629395</v>
       </c>
       <c r="E1833" t="n">
-        <v>39</v>
+        <v>41.7000007629395</v>
       </c>
       <c r="F1833" t="n">
-        <v>34.0999984741211</v>
+        <v>39.0999984741211</v>
       </c>
       <c r="G1833" t="s">
         <v>7</v>
@@ -42533,22 +42533,22 @@
     </row>
     <row r="1834">
       <c r="A1834" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1834" t="n">
-        <v>25000</v>
+        <v>44500</v>
       </c>
       <c r="C1834" t="n">
-        <v>36.5999984741211</v>
+        <v>39</v>
       </c>
       <c r="D1834" t="n">
-        <v>34.4000015258789</v>
+        <v>33</v>
       </c>
       <c r="E1834" t="n">
-        <v>34.4000015258789</v>
+        <v>39</v>
       </c>
       <c r="F1834" t="n">
-        <v>35</v>
+        <v>34.0999984741211</v>
       </c>
       <c r="G1834" t="s">
         <v>7</v>
@@ -42556,22 +42556,22 @@
     </row>
     <row r="1835">
       <c r="A1835" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1835" t="n">
-        <v>16250</v>
+        <v>25000</v>
       </c>
       <c r="C1835" t="n">
-        <v>33.5</v>
+        <v>36.5999984741211</v>
       </c>
       <c r="D1835" t="n">
-        <v>32.2999992370605</v>
+        <v>34.4000015258789</v>
       </c>
       <c r="E1835" t="n">
-        <v>33.2999992370605</v>
+        <v>34.4000015258789</v>
       </c>
       <c r="F1835" t="n">
-        <v>32.5999984741211</v>
+        <v>35</v>
       </c>
       <c r="G1835" t="s">
         <v>7</v>
@@ -42579,22 +42579,22 @@
     </row>
     <row r="1836">
       <c r="A1836" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1836" t="n">
-        <v>19000</v>
+        <v>16250</v>
       </c>
       <c r="C1836" t="n">
         <v>33.5</v>
       </c>
       <c r="D1836" t="n">
-        <v>29.7000007629395</v>
+        <v>32.2999992370605</v>
       </c>
       <c r="E1836" t="n">
-        <v>33.5</v>
+        <v>33.2999992370605</v>
       </c>
       <c r="F1836" t="n">
-        <v>29.7000007629395</v>
+        <v>32.5999984741211</v>
       </c>
       <c r="G1836" t="s">
         <v>7</v>
@@ -42602,22 +42602,22 @@
     </row>
     <row r="1837">
       <c r="A1837" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1837" t="n">
-        <v>55000</v>
+        <v>19000</v>
       </c>
       <c r="C1837" t="n">
-        <v>29.8999996185303</v>
+        <v>33.5</v>
       </c>
       <c r="D1837" t="n">
-        <v>27</v>
+        <v>29.7000007629395</v>
       </c>
       <c r="E1837" t="n">
-        <v>29.8999996185303</v>
+        <v>33.5</v>
       </c>
       <c r="F1837" t="n">
-        <v>27.7999992370605</v>
+        <v>29.7000007629395</v>
       </c>
       <c r="G1837" t="s">
         <v>7</v>
@@ -42625,24 +42625,47 @@
     </row>
     <row r="1838">
       <c r="A1838" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1838" t="n">
-        <v>45250</v>
+        <v>55000</v>
       </c>
       <c r="C1838" t="n">
-        <v>33.5</v>
+        <v>29.8999996185303</v>
       </c>
       <c r="D1838" t="n">
-        <v>27.7000007629395</v>
+        <v>27</v>
       </c>
       <c r="E1838" t="n">
-        <v>27.7000007629395</v>
+        <v>29.8999996185303</v>
       </c>
       <c r="F1838" t="n">
-        <v>34</v>
+        <v>27.7999992370605</v>
       </c>
       <c r="G1838" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>75250</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>33.7999992370605</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>35.4000015258789</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>38.2000007629395</v>
+      </c>
+      <c r="G1839" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48241,6 +48241,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1842">
+      <c r="A1842" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>12250</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>41</v>
+      </c>
+      <c r="H1842" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48267,6 +48267,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1843">
+      <c r="A1843" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>40.7000007629395</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1843" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48293,6 +48293,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>13250</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>42.0999984741211</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="H1844" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48319,6 +48319,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>44.2000007629395</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>43.2000007629395</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1845" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48397,6 +48397,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1848">
+      <c r="A1848" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>16250</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>45.7000007629395</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>42</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H1848" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42938,8 +42938,31 @@
       <c r="E1851" t="n">
         <v>52.2000007629395</v>
       </c>
-      <c r="F1851"/>
+      <c r="F1851" t="n">
+        <v>55.7999992370605</v>
+      </c>
       <c r="G1851" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1852" t="n">
+        <v>50500</v>
+      </c>
+      <c r="C1852" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="D1852" t="n">
+        <v>55</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>56.5999984741211</v>
+      </c>
+      <c r="F1852"/>
+      <c r="G1852" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42961,8 +42961,31 @@
       <c r="E1852" t="n">
         <v>56.5999984741211</v>
       </c>
-      <c r="F1852"/>
+      <c r="F1852" t="n">
+        <v>58.4000015258789</v>
+      </c>
       <c r="G1852" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1853" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1853" t="n">
+        <v>58.2000007629395</v>
+      </c>
+      <c r="D1853" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>57.2000007629395</v>
+      </c>
+      <c r="F1853"/>
+      <c r="G1853" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -42984,8 +42984,31 @@
       <c r="E1853" t="n">
         <v>57.2000007629395</v>
       </c>
-      <c r="F1853"/>
+      <c r="F1853" t="n">
+        <v>57.5999984741211</v>
+      </c>
       <c r="G1853" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1854" t="n">
+        <v>23750</v>
+      </c>
+      <c r="C1854" t="n">
+        <v>58.4000015258789</v>
+      </c>
+      <c r="D1854" t="n">
+        <v>56</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>57.2000007629395</v>
+      </c>
+      <c r="F1854"/>
+      <c r="G1854" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -43007,8 +43007,31 @@
       <c r="E1854" t="n">
         <v>57.2000007629395</v>
       </c>
-      <c r="F1854"/>
+      <c r="F1854" t="n">
+        <v>58.4000015258789</v>
+      </c>
       <c r="G1854" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1855" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1855" t="n">
+        <v>58.4000015258789</v>
+      </c>
+      <c r="D1855" t="n">
+        <v>55.2000007629395</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>57.7999992370605</v>
+      </c>
+      <c r="F1855"/>
+      <c r="G1855" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -43037,6 +43037,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1856">
+      <c r="A1856" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1856" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C1856" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="D1856" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="E1856" t="n">
+        <v>57.2000007629395</v>
+      </c>
+      <c r="F1856" t="n">
+        <v>55.5999984741211</v>
+      </c>
+      <c r="G1856" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48683,6 +48683,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1859">
+      <c r="A1859" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1859" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C1859" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1859" t="n">
+        <v>49.7000007629395</v>
+      </c>
+      <c r="E1859" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="F1859" t="n">
+        <v>51.5999984741211</v>
+      </c>
+      <c r="G1859" t="n">
+        <v>51.5999984741211</v>
+      </c>
+      <c r="H1859" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -48709,6 +48709,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1860">
+      <c r="A1860" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1860" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1860" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="D1860" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="F1860" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="G1860" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="H1860" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54318,6 +54318,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1861">
+      <c r="A1861" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1861" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1861" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="D1861" t="n">
+        <v>58</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="G1861" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="H1861" t="n">
+        <v>18500</v>
+      </c>
+      <c r="I1861" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1862" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1862" t="n">
+        <v>58.4000015258789</v>
+      </c>
+      <c r="D1862" t="n">
+        <v>58.4000015258789</v>
+      </c>
+      <c r="E1862" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1862" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1862" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1862" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I1862" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54376,6 +54376,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1863">
+      <c r="A1863" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1863" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1863" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="D1863" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>51.2000007629395</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>54.5999984741211</v>
+      </c>
+      <c r="G1863" t="n">
+        <v>54.5999984741211</v>
+      </c>
+      <c r="H1863" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I1863" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54405,6 +54405,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1864">
+      <c r="A1864" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1864" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1864" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1864" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>54.7999992370605</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>54.2000007629395</v>
+      </c>
+      <c r="G1864" t="n">
+        <v>54.2000007629395</v>
+      </c>
+      <c r="H1864" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I1864" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54419,7 +54419,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="E1864" t="n">
-        <v>54.7999992370605</v>
+        <v>54.2000007629395</v>
       </c>
       <c r="F1864" t="n">
         <v>54.2000007629395</v>
@@ -54431,6 +54431,35 @@
         <v>8500</v>
       </c>
       <c r="I1864" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1865" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1865" t="n">
+        <v>54.4000015258789</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>55.2000007629395</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>54</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1865" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I1865" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54463,6 +54463,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1866">
+      <c r="A1866" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1866" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1866" t="n">
+        <v>55.7999992370605</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>57.5999984741211</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>55.2000007629395</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="G1866" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="H1866" t="n">
+        <v>7750</v>
+      </c>
+      <c r="I1866" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54477,7 +54477,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="E1866" t="n">
-        <v>55.2000007629395</v>
+        <v>55.5999984741211</v>
       </c>
       <c r="F1866" t="n">
         <v>56.7999992370605</v>
@@ -54489,6 +54489,35 @@
         <v>7750</v>
       </c>
       <c r="I1866" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1867" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1867" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>58</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>56.4000015258789</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>56.4000015258789</v>
+      </c>
+      <c r="H1867" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1867" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54521,6 +54521,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1868">
+      <c r="A1868" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1868" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1868" t="n">
+        <v>56.5999984741211</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>57</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="G1868" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="H1868" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1868" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54550,6 +54550,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1869">
+      <c r="A1869" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1869" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1869" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>56.7999992370605</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>55.2000007629395</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="H1869" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1869" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OS.MI.xlsx
+++ b/data/OS.MI.xlsx
@@ -54579,6 +54579,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1870">
+      <c r="A1870" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1870" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1870" t="n">
+        <v>56.4000015258789</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>56.5999984741211</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>54.4000015258789</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>55.5999984741211</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>55.5999984741211</v>
+      </c>
+      <c r="H1870" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I1870" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
